--- a/Groundtruth/roi_coordinates.xlsx
+++ b/Groundtruth/roi_coordinates.xlsx
@@ -570,7 +570,7 @@
         <v>384</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
